--- a/projects.xlsx
+++ b/projects.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\synechron\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{020C85E9-9EDC-41E1-A36D-F64735C2AAB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04FF75C1-1DC0-4E4D-9C0A-C6DEA1D32C22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{E550C8CF-C2ED-49BD-895D-3DA1DC81D50A}"/>
   </bookViews>
@@ -25,82 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
-  <si>
-    <t>CHINTHALA DURGA PRASAD</t>
-  </si>
-  <si>
-    <t>RACHARLA SAI KRISHNA</t>
-  </si>
-  <si>
-    <t>HANUMANTHU NANI</t>
-  </si>
-  <si>
-    <t>Aman kumar</t>
-  </si>
-  <si>
-    <t>Abhinav Choudhary</t>
-  </si>
-  <si>
-    <t>Ayush Chahal</t>
-  </si>
-  <si>
-    <t>Bandhanatham Hanshika Netha</t>
-  </si>
-  <si>
-    <t>Billa Abijith Chowdary</t>
-  </si>
-  <si>
-    <t>Esha Bhanot</t>
-  </si>
-  <si>
-    <t>More Srinivas</t>
-  </si>
-  <si>
-    <t>Prachi Soni</t>
-  </si>
-  <si>
-    <t>Tanmoy Debnath</t>
-  </si>
-  <si>
-    <t>Aakash</t>
-  </si>
-  <si>
-    <t>Sanjana</t>
-  </si>
-  <si>
-    <t>MD JAMI KHAN</t>
-  </si>
-  <si>
-    <t>Appari Naga Venkata Manikanta Sai Kalyan</t>
-  </si>
-  <si>
-    <t>Akula Hema Venkata Sriram</t>
-  </si>
-  <si>
-    <t>Prateek Raj</t>
-  </si>
-  <si>
-    <t>Kabir Saini</t>
-  </si>
-  <si>
-    <t>Pallapati Pavan Kumar</t>
-  </si>
-  <si>
-    <t>Babalpreet Singh</t>
-  </si>
-  <si>
-    <t>Saksham gupta</t>
-  </si>
-  <si>
-    <t>Arush Gupta</t>
-  </si>
-  <si>
-    <t>Renu Kumari</t>
-  </si>
-  <si>
-    <t>Dheeraj Kumar</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>Job Portal Platform</t>
   </si>
@@ -175,6 +100,51 @@
   </si>
   <si>
     <t>mobile recharge and utility payment platform</t>
+  </si>
+  <si>
+    <t>Bhargavi Choudhary</t>
+  </si>
+  <si>
+    <t>Praneetha</t>
+  </si>
+  <si>
+    <t>Ankush</t>
+  </si>
+  <si>
+    <t>Phanindra</t>
+  </si>
+  <si>
+    <t>Chandana</t>
+  </si>
+  <si>
+    <t>Sicakumaran M</t>
+  </si>
+  <si>
+    <t>Srijan Choudhary</t>
+  </si>
+  <si>
+    <t>Ali Ismail Khan Lohani</t>
+  </si>
+  <si>
+    <t>Sunny Sharma</t>
+  </si>
+  <si>
+    <t>Vikas</t>
+  </si>
+  <si>
+    <t>Gurv Lakhina</t>
+  </si>
+  <si>
+    <t>Jalaj</t>
+  </si>
+  <si>
+    <t>Lakshmi</t>
+  </si>
+  <si>
+    <t>Amrutha BR</t>
+  </si>
+  <si>
+    <t>Kevin</t>
   </si>
 </sst>
 </file>
@@ -575,202 +545,182 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="B1" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" t="s">
         <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>28</v>
-      </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="2"/>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="2"/>
+      <c r="B6" t="s">
         <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A9" s="2"/>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A12" s="2"/>
       <c r="B12" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="A14" s="1"/>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" t="s">
         <v>16</v>
-      </c>
-      <c r="B17" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" t="s">
         <v>17</v>
-      </c>
-      <c r="B18" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" t="s">
         <v>18</v>
-      </c>
-      <c r="B19" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B20" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="1"/>
+      <c r="B22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
+      <c r="B23" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="1"/>
+      <c r="B24" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="1"/>
+      <c r="B25" t="s">
         <v>20</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B24" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B25" t="s">
-        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/projects.xlsx
+++ b/projects.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\synechron\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04FF75C1-1DC0-4E4D-9C0A-C6DEA1D32C22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE642A77-02BE-4361-8D53-FDD9F981E960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{E550C8CF-C2ED-49BD-895D-3DA1DC81D50A}"/>
   </bookViews>
@@ -117,9 +117,6 @@
     <t>Chandana</t>
   </si>
   <si>
-    <t>Sicakumaran M</t>
-  </si>
-  <si>
     <t>Srijan Choudhary</t>
   </si>
   <si>
@@ -145,6 +142,9 @@
   </si>
   <si>
     <t>Kevin</t>
+  </si>
+  <si>
+    <t>Sivakumaran M</t>
   </si>
 </sst>
 </file>
@@ -545,7 +545,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B1" t="s">
         <v>8</v>
@@ -567,7 +567,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B4" t="s">
         <v>3</v>
@@ -587,7 +587,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B7" t="s">
         <v>2</v>
@@ -595,7 +595,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>21</v>
@@ -617,7 +617,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
@@ -631,7 +631,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B13" t="s">
         <v>10</v>
@@ -653,7 +653,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B16" t="s">
         <v>7</v>
@@ -661,7 +661,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B17" t="s">
         <v>16</v>
@@ -685,7 +685,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B20" t="s">
         <v>9</v>
@@ -693,7 +693,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>22</v>
